--- a/Electronics/PCBs/Main/PickAndPlace.xlsx
+++ b/Electronics/PCBs/Main/PickAndPlace.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="PickAndPlace_PCB-V1_2026-03-05" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="PickAndPlace_PCB-V1_2026-03-30" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="285">
   <si>
     <t>Designator</t>
   </si>
@@ -854,6 +854,18 @@
   </si>
   <si>
     <t>15.747mm</t>
+  </si>
+  <si>
+    <t>CUPEN</t>
+  </si>
+  <si>
+    <t>47mm</t>
+  </si>
+  <si>
+    <t>-2mm</t>
+  </si>
+  <si>
+    <t>46.3mm</t>
   </si>
 </sst>
 </file>
@@ -1230,7 +1242,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N61"/>
+  <dimension ref="A1:N62"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="14" width="20" customWidth="1"/>
@@ -3920,6 +3932,50 @@
         <v>278</v>
       </c>
     </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>281</v>
+      </c>
+      <c r="B62" t="s">
+        <v>75</v>
+      </c>
+      <c r="C62" t="s">
+        <v>53</v>
+      </c>
+      <c r="D62" t="s">
+        <v>282</v>
+      </c>
+      <c r="E62" t="s">
+        <v>283</v>
+      </c>
+      <c r="F62" t="s">
+        <v>282</v>
+      </c>
+      <c r="G62" t="s">
+        <v>283</v>
+      </c>
+      <c r="H62" t="s">
+        <v>284</v>
+      </c>
+      <c r="I62" t="s">
+        <v>283</v>
+      </c>
+      <c r="J62">
+        <v>2</v>
+      </c>
+      <c r="K62" t="s">
+        <v>21</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62" t="s">
+        <v>22</v>
+      </c>
+      <c r="N62" t="s">
+        <v>79</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Electronics/PCBs/Main/PickAndPlace.xlsx
+++ b/Electronics/PCBs/Main/PickAndPlace.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="PickAndPlace_PCB-V1_2026-03-30" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="PickAndPlace_PCB-V1_2026-04-29" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="289">
   <si>
     <t>Designator</t>
   </si>
@@ -244,7 +244,7 @@
     <t>13.4mm</t>
   </si>
   <si>
-    <t>-26.2mm</t>
+    <t>-27.7mm</t>
   </si>
   <si>
     <t>12.7mm</t>
@@ -400,9 +400,6 @@
     <t>2.6mm</t>
   </si>
   <si>
-    <t>-27.7mm</t>
-  </si>
-  <si>
     <t>1.9mm</t>
   </si>
   <si>
@@ -694,7 +691,7 @@
     <t>41.153mm</t>
   </si>
   <si>
-    <t>RUPEN</t>
+    <t>RUPEN1</t>
   </si>
   <si>
     <t>22.8mm</t>
@@ -760,112 +757,127 @@
     <t>21.8mm</t>
   </si>
   <si>
+    <t>CINL</t>
+  </si>
+  <si>
+    <t>-25.9mm</t>
+  </si>
+  <si>
+    <t>3.3mm</t>
+  </si>
+  <si>
+    <t>CAVDD</t>
+  </si>
+  <si>
+    <t>1.405mm</t>
+  </si>
+  <si>
+    <t>-22.994mm</t>
+  </si>
+  <si>
+    <t>-22.294mm</t>
+  </si>
+  <si>
+    <t>CSPKR</t>
+  </si>
+  <si>
+    <t>-16.7mm</t>
+  </si>
+  <si>
+    <t>7.3mm</t>
+  </si>
+  <si>
+    <t>LAVDD</t>
+  </si>
+  <si>
+    <t>BLM18SG121TN1D</t>
+  </si>
+  <si>
+    <t>L0603</t>
+  </si>
+  <si>
+    <t>3.1mm</t>
+  </si>
+  <si>
+    <t>-23.7mm</t>
+  </si>
+  <si>
+    <t>LSPKRG</t>
+  </si>
+  <si>
+    <t>7mm</t>
+  </si>
+  <si>
+    <t>-14mm</t>
+  </si>
+  <si>
+    <t>-14.7mm</t>
+  </si>
+  <si>
+    <t>LSPKRV</t>
+  </si>
+  <si>
+    <t>RCAM17</t>
+  </si>
+  <si>
+    <t>RC0603FR-071KL</t>
+  </si>
+  <si>
+    <t>-47.753mm</t>
+  </si>
+  <si>
+    <t>1kΩ</t>
+  </si>
+  <si>
+    <t>RINR</t>
+  </si>
+  <si>
+    <t>15.8mm</t>
+  </si>
+  <si>
+    <t>-28.9mm</t>
+  </si>
+  <si>
+    <t>-29.653mm</t>
+  </si>
+  <si>
+    <t>CUPEN1</t>
+  </si>
+  <si>
+    <t>47mm</t>
+  </si>
+  <si>
+    <t>-2mm</t>
+  </si>
+  <si>
+    <t>47.7mm</t>
+  </si>
+  <si>
     <t>CINR2</t>
   </si>
   <si>
-    <t>-28.1mm</t>
-  </si>
-  <si>
-    <t>CINL</t>
-  </si>
-  <si>
-    <t>-25.9mm</t>
-  </si>
-  <si>
-    <t>3.3mm</t>
-  </si>
-  <si>
-    <t>CAVDD</t>
-  </si>
-  <si>
-    <t>1.405mm</t>
-  </si>
-  <si>
-    <t>-22.994mm</t>
-  </si>
-  <si>
-    <t>-22.294mm</t>
-  </si>
-  <si>
-    <t>CSPKR</t>
-  </si>
-  <si>
-    <t>-16.7mm</t>
-  </si>
-  <si>
-    <t>7.3mm</t>
-  </si>
-  <si>
-    <t>CASIG</t>
-  </si>
-  <si>
-    <t>CL10B473KB8NNNC</t>
-  </si>
-  <si>
-    <t>-32mm</t>
-  </si>
-  <si>
-    <t>7mm</t>
-  </si>
-  <si>
-    <t>47nF</t>
-  </si>
-  <si>
-    <t>LAVDD</t>
-  </si>
-  <si>
-    <t>BLM18SG121TN1D</t>
-  </si>
-  <si>
-    <t>L0603</t>
-  </si>
-  <si>
-    <t>3.1mm</t>
-  </si>
-  <si>
-    <t>-23.7mm</t>
-  </si>
-  <si>
-    <t>LSPKRG</t>
-  </si>
-  <si>
-    <t>-14mm</t>
-  </si>
-  <si>
-    <t>-14.7mm</t>
-  </si>
-  <si>
-    <t>LSPKRV</t>
-  </si>
-  <si>
-    <t>RCAM17</t>
-  </si>
-  <si>
-    <t>RC0603FR-071KL</t>
-  </si>
-  <si>
-    <t>-47.753mm</t>
-  </si>
-  <si>
-    <t>1kΩ</t>
-  </si>
-  <si>
-    <t>RINR</t>
-  </si>
-  <si>
-    <t>15.747mm</t>
-  </si>
-  <si>
-    <t>CUPEN</t>
-  </si>
-  <si>
-    <t>47mm</t>
-  </si>
-  <si>
-    <t>-2mm</t>
-  </si>
-  <si>
-    <t>46.3mm</t>
+    <t>0603B103K500NT</t>
+  </si>
+  <si>
+    <t>-29.5mm</t>
+  </si>
+  <si>
+    <t>10nF</t>
+  </si>
+  <si>
+    <t>RPAM</t>
+  </si>
+  <si>
+    <t>0603WAF2202T5E</t>
+  </si>
+  <si>
+    <t>-26mm</t>
+  </si>
+  <si>
+    <t>12.647mm</t>
+  </si>
+  <si>
+    <t>22kΩ</t>
   </si>
 </sst>
 </file>
@@ -2318,19 +2330,19 @@
         <v>128</v>
       </c>
       <c r="E25" t="s">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="F25" t="s">
         <v>128</v>
       </c>
       <c r="G25" t="s">
+        <v>77</v>
+      </c>
+      <c r="H25" t="s">
         <v>129</v>
       </c>
-      <c r="H25" t="s">
-        <v>130</v>
-      </c>
       <c r="I25" t="s">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="J25">
         <v>2</v>
@@ -2350,31 +2362,31 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>130</v>
+      </c>
+      <c r="B26" t="s">
         <v>131</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>132</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>133</v>
-      </c>
-      <c r="D26" t="s">
-        <v>134</v>
       </c>
       <c r="E26" t="s">
         <v>27</v>
       </c>
       <c r="F26" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G26" t="s">
         <v>27</v>
       </c>
       <c r="H26" t="s">
+        <v>133</v>
+      </c>
+      <c r="I26" t="s">
         <v>134</v>
-      </c>
-      <c r="I26" t="s">
-        <v>135</v>
       </c>
       <c r="J26">
         <v>2</v>
@@ -2389,36 +2401,36 @@
         <v>22</v>
       </c>
       <c r="N26" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>136</v>
+      </c>
+      <c r="B27" t="s">
+        <v>131</v>
+      </c>
+      <c r="C27" t="s">
+        <v>132</v>
+      </c>
+      <c r="D27" t="s">
         <v>137</v>
-      </c>
-      <c r="B27" t="s">
-        <v>132</v>
-      </c>
-      <c r="C27" t="s">
-        <v>133</v>
-      </c>
-      <c r="D27" t="s">
-        <v>138</v>
       </c>
       <c r="E27" t="s">
         <v>27</v>
       </c>
       <c r="F27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G27" t="s">
         <v>27</v>
       </c>
       <c r="H27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I27" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J27">
         <v>2</v>
@@ -2433,36 +2445,36 @@
         <v>22</v>
       </c>
       <c r="N27" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>138</v>
+      </c>
+      <c r="B28" t="s">
         <v>139</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>140</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>141</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>142</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
+        <v>141</v>
+      </c>
+      <c r="G28" t="s">
+        <v>142</v>
+      </c>
+      <c r="H28" t="s">
         <v>143</v>
       </c>
-      <c r="F28" t="s">
-        <v>142</v>
-      </c>
-      <c r="G28" t="s">
-        <v>143</v>
-      </c>
-      <c r="H28" t="s">
+      <c r="I28" t="s">
         <v>144</v>
-      </c>
-      <c r="I28" t="s">
-        <v>145</v>
       </c>
       <c r="J28">
         <v>49</v>
@@ -2477,12 +2489,12 @@
         <v>22</v>
       </c>
       <c r="N28" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B29" t="s">
         <v>99</v>
@@ -2491,19 +2503,19 @@
         <v>100</v>
       </c>
       <c r="D29" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E29" t="s">
         <v>43</v>
       </c>
       <c r="F29" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G29" t="s">
         <v>43</v>
       </c>
       <c r="H29" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I29" t="s">
         <v>39</v>
@@ -2526,31 +2538,31 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>147</v>
+      </c>
+      <c r="B30" t="s">
         <v>148</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>149</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>150</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>151</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
+        <v>150</v>
+      </c>
+      <c r="G30" t="s">
+        <v>151</v>
+      </c>
+      <c r="H30" t="s">
         <v>152</v>
       </c>
-      <c r="F30" t="s">
-        <v>151</v>
-      </c>
-      <c r="G30" t="s">
-        <v>152</v>
-      </c>
-      <c r="H30" t="s">
+      <c r="I30" t="s">
         <v>153</v>
-      </c>
-      <c r="I30" t="s">
-        <v>154</v>
       </c>
       <c r="J30">
         <v>16</v>
@@ -2565,36 +2577,36 @@
         <v>22</v>
       </c>
       <c r="N30" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>154</v>
+      </c>
+      <c r="B31" t="s">
         <v>155</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>156</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>157</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>158</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
+        <v>157</v>
+      </c>
+      <c r="G31" t="s">
+        <v>158</v>
+      </c>
+      <c r="H31" t="s">
         <v>159</v>
       </c>
-      <c r="F31" t="s">
-        <v>158</v>
-      </c>
-      <c r="G31" t="s">
-        <v>159</v>
-      </c>
-      <c r="H31" t="s">
+      <c r="I31" t="s">
         <v>160</v>
-      </c>
-      <c r="I31" t="s">
-        <v>161</v>
       </c>
       <c r="J31">
         <v>3</v>
@@ -2609,36 +2621,36 @@
         <v>22</v>
       </c>
       <c r="N31" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>161</v>
+      </c>
+      <c r="B32" t="s">
+        <v>155</v>
+      </c>
+      <c r="C32" t="s">
+        <v>156</v>
+      </c>
+      <c r="D32" t="s">
         <v>162</v>
       </c>
-      <c r="B32" t="s">
-        <v>156</v>
-      </c>
-      <c r="C32" t="s">
-        <v>157</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
+        <v>158</v>
+      </c>
+      <c r="F32" t="s">
+        <v>162</v>
+      </c>
+      <c r="G32" t="s">
+        <v>158</v>
+      </c>
+      <c r="H32" t="s">
         <v>163</v>
       </c>
-      <c r="E32" t="s">
-        <v>159</v>
-      </c>
-      <c r="F32" t="s">
-        <v>163</v>
-      </c>
-      <c r="G32" t="s">
-        <v>159</v>
-      </c>
-      <c r="H32" t="s">
+      <c r="I32" t="s">
         <v>164</v>
-      </c>
-      <c r="I32" t="s">
-        <v>165</v>
       </c>
       <c r="J32">
         <v>3</v>
@@ -2653,36 +2665,36 @@
         <v>22</v>
       </c>
       <c r="N32" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>165</v>
+      </c>
+      <c r="B33" t="s">
         <v>166</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>167</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>168</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>169</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
+        <v>168</v>
+      </c>
+      <c r="G33" t="s">
+        <v>169</v>
+      </c>
+      <c r="H33" t="s">
         <v>170</v>
       </c>
-      <c r="F33" t="s">
+      <c r="I33" t="s">
         <v>169</v>
-      </c>
-      <c r="G33" t="s">
-        <v>170</v>
-      </c>
-      <c r="H33" t="s">
-        <v>171</v>
-      </c>
-      <c r="I33" t="s">
-        <v>170</v>
       </c>
       <c r="J33">
         <v>2</v>
@@ -2697,36 +2709,36 @@
         <v>22</v>
       </c>
       <c r="N33" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>172</v>
+      </c>
+      <c r="B34" t="s">
+        <v>166</v>
+      </c>
+      <c r="C34" t="s">
+        <v>167</v>
+      </c>
+      <c r="D34" t="s">
+        <v>168</v>
+      </c>
+      <c r="E34" t="s">
         <v>173</v>
       </c>
-      <c r="B34" t="s">
-        <v>167</v>
-      </c>
-      <c r="C34" t="s">
+      <c r="F34" t="s">
         <v>168</v>
       </c>
-      <c r="D34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E34" t="s">
-        <v>174</v>
-      </c>
-      <c r="F34" t="s">
-        <v>169</v>
-      </c>
       <c r="G34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H34" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J34">
         <v>2</v>
@@ -2741,36 +2753,36 @@
         <v>22</v>
       </c>
       <c r="N34" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>174</v>
+      </c>
+      <c r="B35" t="s">
+        <v>166</v>
+      </c>
+      <c r="C35" t="s">
+        <v>167</v>
+      </c>
+      <c r="D35" t="s">
+        <v>168</v>
+      </c>
+      <c r="E35" t="s">
         <v>175</v>
       </c>
-      <c r="B35" t="s">
-        <v>167</v>
-      </c>
-      <c r="C35" t="s">
+      <c r="F35" t="s">
         <v>168</v>
       </c>
-      <c r="D35" t="s">
-        <v>169</v>
-      </c>
-      <c r="E35" t="s">
-        <v>176</v>
-      </c>
-      <c r="F35" t="s">
-        <v>169</v>
-      </c>
       <c r="G35" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H35" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I35" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J35">
         <v>2</v>
@@ -2785,36 +2797,36 @@
         <v>22</v>
       </c>
       <c r="N35" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>176</v>
+      </c>
+      <c r="B36" t="s">
+        <v>166</v>
+      </c>
+      <c r="C36" t="s">
+        <v>167</v>
+      </c>
+      <c r="D36" t="s">
+        <v>168</v>
+      </c>
+      <c r="E36" t="s">
         <v>177</v>
       </c>
-      <c r="B36" t="s">
-        <v>167</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="F36" t="s">
         <v>168</v>
       </c>
-      <c r="D36" t="s">
-        <v>169</v>
-      </c>
-      <c r="E36" t="s">
-        <v>178</v>
-      </c>
-      <c r="F36" t="s">
-        <v>169</v>
-      </c>
       <c r="G36" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H36" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I36" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J36">
         <v>2</v>
@@ -2829,36 +2841,36 @@
         <v>22</v>
       </c>
       <c r="N36" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>178</v>
+      </c>
+      <c r="B37" t="s">
         <v>179</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>180</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
+        <v>150</v>
+      </c>
+      <c r="E37" t="s">
         <v>181</v>
       </c>
-      <c r="D37" t="s">
-        <v>151</v>
-      </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
+        <v>150</v>
+      </c>
+      <c r="G37" t="s">
+        <v>181</v>
+      </c>
+      <c r="H37" t="s">
         <v>182</v>
       </c>
-      <c r="F37" t="s">
-        <v>151</v>
-      </c>
-      <c r="G37" t="s">
-        <v>182</v>
-      </c>
-      <c r="H37" t="s">
-        <v>183</v>
-      </c>
       <c r="I37" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J37">
         <v>2</v>
@@ -2873,36 +2885,36 @@
         <v>40</v>
       </c>
       <c r="N37" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>183</v>
+      </c>
+      <c r="B38" t="s">
         <v>184</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>185</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>186</v>
-      </c>
-      <c r="D38" t="s">
-        <v>187</v>
       </c>
       <c r="E38" t="s">
         <v>104</v>
       </c>
       <c r="F38" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G38" t="s">
         <v>104</v>
       </c>
       <c r="H38" t="s">
+        <v>187</v>
+      </c>
+      <c r="I38" t="s">
         <v>188</v>
-      </c>
-      <c r="I38" t="s">
-        <v>189</v>
       </c>
       <c r="J38">
         <v>16</v>
@@ -2917,36 +2929,36 @@
         <v>40</v>
       </c>
       <c r="N38" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>189</v>
+      </c>
+      <c r="B39" t="s">
         <v>190</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>191</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
         <v>192</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>193</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
+        <v>192</v>
+      </c>
+      <c r="G39" t="s">
+        <v>193</v>
+      </c>
+      <c r="H39" t="s">
         <v>194</v>
       </c>
-      <c r="F39" t="s">
-        <v>193</v>
-      </c>
-      <c r="G39" t="s">
-        <v>194</v>
-      </c>
-      <c r="H39" t="s">
+      <c r="I39" t="s">
         <v>195</v>
-      </c>
-      <c r="I39" t="s">
-        <v>196</v>
       </c>
       <c r="J39">
         <v>6</v>
@@ -2961,36 +2973,36 @@
         <v>22</v>
       </c>
       <c r="N39" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>197</v>
+      </c>
+      <c r="B40" t="s">
         <v>198</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>199</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>200</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
         <v>201</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
+        <v>200</v>
+      </c>
+      <c r="G40" t="s">
+        <v>201</v>
+      </c>
+      <c r="H40" t="s">
         <v>202</v>
       </c>
-      <c r="F40" t="s">
-        <v>201</v>
-      </c>
-      <c r="G40" t="s">
-        <v>202</v>
-      </c>
-      <c r="H40" t="s">
+      <c r="I40" t="s">
         <v>203</v>
-      </c>
-      <c r="I40" t="s">
-        <v>204</v>
       </c>
       <c r="J40">
         <v>3</v>
@@ -3005,36 +3017,36 @@
         <v>22</v>
       </c>
       <c r="N40" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>205</v>
+      </c>
+      <c r="B41" t="s">
         <v>206</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>207</v>
       </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
+        <v>200</v>
+      </c>
+      <c r="E41" t="s">
         <v>208</v>
       </c>
-      <c r="D41" t="s">
-        <v>201</v>
-      </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
+        <v>200</v>
+      </c>
+      <c r="G41" t="s">
+        <v>208</v>
+      </c>
+      <c r="H41" t="s">
         <v>209</v>
       </c>
-      <c r="F41" t="s">
-        <v>201</v>
-      </c>
-      <c r="G41" t="s">
-        <v>209</v>
-      </c>
-      <c r="H41" t="s">
+      <c r="I41" t="s">
         <v>210</v>
-      </c>
-      <c r="I41" t="s">
-        <v>211</v>
       </c>
       <c r="J41">
         <v>3</v>
@@ -3049,33 +3061,33 @@
         <v>22</v>
       </c>
       <c r="N41" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>211</v>
+      </c>
+      <c r="B42" t="s">
         <v>212</v>
-      </c>
-      <c r="B42" t="s">
-        <v>213</v>
       </c>
       <c r="C42" t="s">
         <v>53</v>
       </c>
       <c r="D42" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E42" t="s">
         <v>55</v>
       </c>
       <c r="F42" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G42" t="s">
         <v>55</v>
       </c>
       <c r="H42" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I42" t="s">
         <v>56</v>
@@ -3093,33 +3105,33 @@
         <v>22</v>
       </c>
       <c r="N42" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B43" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C43" t="s">
         <v>53</v>
       </c>
       <c r="D43" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E43" t="s">
         <v>63</v>
       </c>
       <c r="F43" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G43" t="s">
         <v>63</v>
       </c>
       <c r="H43" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I43" t="s">
         <v>64</v>
@@ -3137,15 +3149,15 @@
         <v>22</v>
       </c>
       <c r="N43" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B44" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C44" t="s">
         <v>53</v>
@@ -3154,19 +3166,19 @@
         <v>66</v>
       </c>
       <c r="E44" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F44" t="s">
         <v>66</v>
       </c>
       <c r="G44" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H44" t="s">
         <v>68</v>
       </c>
       <c r="I44" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J44">
         <v>2</v>
@@ -3181,36 +3193,36 @@
         <v>22</v>
       </c>
       <c r="N44" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>218</v>
+      </c>
+      <c r="B45" t="s">
         <v>219</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
+        <v>167</v>
+      </c>
+      <c r="D45" t="s">
+        <v>192</v>
+      </c>
+      <c r="E45" t="s">
         <v>220</v>
       </c>
-      <c r="C45" t="s">
-        <v>168</v>
-      </c>
-      <c r="D45" t="s">
-        <v>193</v>
-      </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
+        <v>192</v>
+      </c>
+      <c r="G45" t="s">
+        <v>220</v>
+      </c>
+      <c r="H45" t="s">
         <v>221</v>
       </c>
-      <c r="F45" t="s">
-        <v>193</v>
-      </c>
-      <c r="G45" t="s">
-        <v>221</v>
-      </c>
-      <c r="H45" t="s">
-        <v>222</v>
-      </c>
       <c r="I45" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J45">
         <v>2</v>
@@ -3225,36 +3237,36 @@
         <v>22</v>
       </c>
       <c r="N45" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>223</v>
+      </c>
+      <c r="B46" t="s">
+        <v>219</v>
+      </c>
+      <c r="C46" t="s">
+        <v>167</v>
+      </c>
+      <c r="D46" t="s">
+        <v>192</v>
+      </c>
+      <c r="E46" t="s">
         <v>224</v>
       </c>
-      <c r="B46" t="s">
-        <v>220</v>
-      </c>
-      <c r="C46" t="s">
-        <v>168</v>
-      </c>
-      <c r="D46" t="s">
-        <v>193</v>
-      </c>
-      <c r="E46" t="s">
+      <c r="F46" t="s">
+        <v>192</v>
+      </c>
+      <c r="G46" t="s">
+        <v>224</v>
+      </c>
+      <c r="H46" t="s">
         <v>225</v>
       </c>
-      <c r="F46" t="s">
-        <v>193</v>
-      </c>
-      <c r="G46" t="s">
-        <v>225</v>
-      </c>
-      <c r="H46" t="s">
-        <v>226</v>
-      </c>
       <c r="I46" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J46">
         <v>2</v>
@@ -3269,36 +3281,36 @@
         <v>22</v>
       </c>
       <c r="N46" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>226</v>
+      </c>
+      <c r="B47" t="s">
+        <v>219</v>
+      </c>
+      <c r="C47" t="s">
+        <v>167</v>
+      </c>
+      <c r="D47" t="s">
         <v>227</v>
       </c>
-      <c r="B47" t="s">
-        <v>220</v>
-      </c>
-      <c r="C47" t="s">
-        <v>168</v>
-      </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
         <v>228</v>
       </c>
-      <c r="E47" t="s">
+      <c r="F47" t="s">
+        <v>227</v>
+      </c>
+      <c r="G47" t="s">
+        <v>228</v>
+      </c>
+      <c r="H47" t="s">
+        <v>227</v>
+      </c>
+      <c r="I47" t="s">
         <v>229</v>
-      </c>
-      <c r="F47" t="s">
-        <v>228</v>
-      </c>
-      <c r="G47" t="s">
-        <v>229</v>
-      </c>
-      <c r="H47" t="s">
-        <v>228</v>
-      </c>
-      <c r="I47" t="s">
-        <v>230</v>
       </c>
       <c r="J47">
         <v>2</v>
@@ -3313,36 +3325,36 @@
         <v>22</v>
       </c>
       <c r="N47" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B48" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C48" t="s">
         <v>53</v>
       </c>
       <c r="D48" t="s">
+        <v>231</v>
+      </c>
+      <c r="E48" t="s">
         <v>232</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
+        <v>231</v>
+      </c>
+      <c r="G48" t="s">
+        <v>232</v>
+      </c>
+      <c r="H48" t="s">
         <v>233</v>
       </c>
-      <c r="F48" t="s">
+      <c r="I48" t="s">
         <v>232</v>
-      </c>
-      <c r="G48" t="s">
-        <v>233</v>
-      </c>
-      <c r="H48" t="s">
-        <v>234</v>
-      </c>
-      <c r="I48" t="s">
-        <v>233</v>
       </c>
       <c r="J48">
         <v>2</v>
@@ -3357,36 +3369,36 @@
         <v>22</v>
       </c>
       <c r="N48" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>234</v>
+      </c>
+      <c r="B49" t="s">
         <v>235</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
+        <v>167</v>
+      </c>
+      <c r="D49" t="s">
+        <v>231</v>
+      </c>
+      <c r="E49" t="s">
         <v>236</v>
       </c>
-      <c r="C49" t="s">
-        <v>168</v>
-      </c>
-      <c r="D49" t="s">
-        <v>232</v>
-      </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
+        <v>231</v>
+      </c>
+      <c r="G49" t="s">
+        <v>236</v>
+      </c>
+      <c r="H49" t="s">
         <v>237</v>
       </c>
-      <c r="F49" t="s">
-        <v>232</v>
-      </c>
-      <c r="G49" t="s">
-        <v>237</v>
-      </c>
-      <c r="H49" t="s">
-        <v>238</v>
-      </c>
       <c r="I49" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J49">
         <v>2</v>
@@ -3401,36 +3413,36 @@
         <v>22</v>
       </c>
       <c r="N49" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>239</v>
+      </c>
+      <c r="B50" t="s">
         <v>240</v>
-      </c>
-      <c r="B50" t="s">
-        <v>241</v>
       </c>
       <c r="C50" t="s">
         <v>53</v>
       </c>
       <c r="D50" t="s">
+        <v>241</v>
+      </c>
+      <c r="E50" t="s">
         <v>242</v>
       </c>
-      <c r="E50" t="s">
+      <c r="F50" t="s">
+        <v>241</v>
+      </c>
+      <c r="G50" t="s">
+        <v>242</v>
+      </c>
+      <c r="H50" t="s">
         <v>243</v>
       </c>
-      <c r="F50" t="s">
+      <c r="I50" t="s">
         <v>242</v>
-      </c>
-      <c r="G50" t="s">
-        <v>243</v>
-      </c>
-      <c r="H50" t="s">
-        <v>244</v>
-      </c>
-      <c r="I50" t="s">
-        <v>243</v>
       </c>
       <c r="J50">
         <v>2</v>
@@ -3445,36 +3457,36 @@
         <v>22</v>
       </c>
       <c r="N50" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B51" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C51" t="s">
         <v>53</v>
       </c>
       <c r="D51" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E51" t="s">
+        <v>246</v>
+      </c>
+      <c r="F51" t="s">
+        <v>241</v>
+      </c>
+      <c r="G51" t="s">
+        <v>246</v>
+      </c>
+      <c r="H51" t="s">
         <v>247</v>
       </c>
-      <c r="F51" t="s">
-        <v>242</v>
-      </c>
-      <c r="G51" t="s">
-        <v>247</v>
-      </c>
-      <c r="H51" t="s">
-        <v>248</v>
-      </c>
       <c r="I51" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="J51">
         <v>2</v>
@@ -3489,36 +3501,36 @@
         <v>22</v>
       </c>
       <c r="N51" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B52" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C52" t="s">
         <v>53</v>
       </c>
       <c r="D52" t="s">
-        <v>76</v>
+        <v>128</v>
       </c>
       <c r="E52" t="s">
+        <v>249</v>
+      </c>
+      <c r="F52" t="s">
+        <v>128</v>
+      </c>
+      <c r="G52" t="s">
+        <v>249</v>
+      </c>
+      <c r="H52" t="s">
         <v>250</v>
       </c>
-      <c r="F52" t="s">
-        <v>76</v>
-      </c>
-      <c r="G52" t="s">
-        <v>250</v>
-      </c>
-      <c r="H52" t="s">
-        <v>78</v>
-      </c>
       <c r="I52" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J52">
         <v>2</v>
@@ -3527,13 +3539,13 @@
         <v>21</v>
       </c>
       <c r="L52">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M52" t="s">
         <v>22</v>
       </c>
       <c r="N52" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
@@ -3541,28 +3553,28 @@
         <v>251</v>
       </c>
       <c r="B53" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C53" t="s">
         <v>53</v>
       </c>
       <c r="D53" t="s">
-        <v>128</v>
+        <v>252</v>
       </c>
       <c r="E53" t="s">
+        <v>253</v>
+      </c>
+      <c r="F53" t="s">
         <v>252</v>
       </c>
-      <c r="F53" t="s">
-        <v>128</v>
-      </c>
       <c r="G53" t="s">
+        <v>253</v>
+      </c>
+      <c r="H53" t="s">
         <v>252</v>
       </c>
-      <c r="H53" t="s">
-        <v>253</v>
-      </c>
       <c r="I53" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="J53">
         <v>2</v>
@@ -3571,42 +3583,42 @@
         <v>21</v>
       </c>
       <c r="L53">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="M53" t="s">
         <v>22</v>
       </c>
       <c r="N53" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B54" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C54" t="s">
         <v>53</v>
       </c>
       <c r="D54" t="s">
-        <v>255</v>
+        <v>150</v>
       </c>
       <c r="E54" t="s">
         <v>256</v>
       </c>
       <c r="F54" t="s">
-        <v>255</v>
+        <v>150</v>
       </c>
       <c r="G54" t="s">
         <v>256</v>
       </c>
       <c r="H54" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="I54" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J54">
         <v>2</v>
@@ -3615,13 +3627,13 @@
         <v>21</v>
       </c>
       <c r="L54">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M54" t="s">
         <v>22</v>
       </c>
       <c r="N54" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
@@ -3629,28 +3641,28 @@
         <v>258</v>
       </c>
       <c r="B55" t="s">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="C55" t="s">
-        <v>53</v>
+        <v>260</v>
       </c>
       <c r="D55" t="s">
+        <v>261</v>
+      </c>
+      <c r="E55" t="s">
         <v>151</v>
       </c>
-      <c r="E55" t="s">
-        <v>259</v>
-      </c>
       <c r="F55" t="s">
+        <v>261</v>
+      </c>
+      <c r="G55" t="s">
         <v>151</v>
       </c>
-      <c r="G55" t="s">
-        <v>259</v>
-      </c>
       <c r="H55" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I55" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="J55">
         <v>2</v>
@@ -3659,42 +3671,42 @@
         <v>21</v>
       </c>
       <c r="L55">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M55" t="s">
         <v>22</v>
       </c>
       <c r="N55" t="s">
-        <v>215</v>
+        <v>259</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B56" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C56" t="s">
-        <v>53</v>
+        <v>260</v>
       </c>
       <c r="D56" t="s">
-        <v>121</v>
+        <v>264</v>
       </c>
       <c r="E56" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F56" t="s">
-        <v>121</v>
+        <v>264</v>
       </c>
       <c r="G56" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H56" t="s">
         <v>264</v>
       </c>
       <c r="I56" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="J56">
         <v>2</v>
@@ -3703,42 +3715,42 @@
         <v>21</v>
       </c>
       <c r="L56">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="M56" t="s">
         <v>22</v>
       </c>
       <c r="N56" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>267</v>
+      </c>
+      <c r="B57" t="s">
+        <v>259</v>
+      </c>
+      <c r="C57" t="s">
+        <v>260</v>
+      </c>
+      <c r="D57" t="s">
+        <v>108</v>
+      </c>
+      <c r="E57" t="s">
+        <v>265</v>
+      </c>
+      <c r="F57" t="s">
+        <v>108</v>
+      </c>
+      <c r="G57" t="s">
+        <v>265</v>
+      </c>
+      <c r="H57" t="s">
+        <v>108</v>
+      </c>
+      <c r="I57" t="s">
         <v>266</v>
-      </c>
-      <c r="B57" t="s">
-        <v>267</v>
-      </c>
-      <c r="C57" t="s">
-        <v>268</v>
-      </c>
-      <c r="D57" t="s">
-        <v>269</v>
-      </c>
-      <c r="E57" t="s">
-        <v>152</v>
-      </c>
-      <c r="F57" t="s">
-        <v>269</v>
-      </c>
-      <c r="G57" t="s">
-        <v>152</v>
-      </c>
-      <c r="H57" t="s">
-        <v>269</v>
-      </c>
-      <c r="I57" t="s">
-        <v>270</v>
       </c>
       <c r="J57">
         <v>2</v>
@@ -3753,36 +3765,36 @@
         <v>22</v>
       </c>
       <c r="N57" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B58" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C58" t="s">
-        <v>268</v>
+        <v>167</v>
       </c>
       <c r="D58" t="s">
-        <v>264</v>
+        <v>233</v>
       </c>
       <c r="E58" t="s">
-        <v>272</v>
+        <v>39</v>
       </c>
       <c r="F58" t="s">
-        <v>264</v>
+        <v>233</v>
       </c>
       <c r="G58" t="s">
-        <v>272</v>
+        <v>39</v>
       </c>
       <c r="H58" t="s">
-        <v>264</v>
+        <v>233</v>
       </c>
       <c r="I58" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="J58">
         <v>2</v>
@@ -3797,36 +3809,36 @@
         <v>22</v>
       </c>
       <c r="N58" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>272</v>
+      </c>
+      <c r="B59" t="s">
+        <v>269</v>
+      </c>
+      <c r="C59" t="s">
+        <v>167</v>
+      </c>
+      <c r="D59" t="s">
+        <v>273</v>
+      </c>
+      <c r="E59" t="s">
         <v>274</v>
       </c>
-      <c r="B59" t="s">
-        <v>267</v>
-      </c>
-      <c r="C59" t="s">
-        <v>268</v>
-      </c>
-      <c r="D59" t="s">
-        <v>108</v>
-      </c>
-      <c r="E59" t="s">
-        <v>272</v>
-      </c>
       <c r="F59" t="s">
-        <v>108</v>
+        <v>273</v>
       </c>
       <c r="G59" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="H59" t="s">
-        <v>108</v>
+        <v>273</v>
       </c>
       <c r="I59" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="J59">
         <v>2</v>
@@ -3841,36 +3853,36 @@
         <v>22</v>
       </c>
       <c r="N59" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B60" t="s">
-        <v>276</v>
+        <v>75</v>
       </c>
       <c r="C60" t="s">
-        <v>168</v>
+        <v>53</v>
       </c>
       <c r="D60" t="s">
-        <v>234</v>
+        <v>277</v>
       </c>
       <c r="E60" t="s">
-        <v>39</v>
+        <v>278</v>
       </c>
       <c r="F60" t="s">
-        <v>234</v>
+        <v>277</v>
       </c>
       <c r="G60" t="s">
-        <v>39</v>
+        <v>278</v>
       </c>
       <c r="H60" t="s">
-        <v>234</v>
+        <v>279</v>
       </c>
       <c r="I60" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J60">
         <v>2</v>
@@ -3879,42 +3891,42 @@
         <v>21</v>
       </c>
       <c r="L60">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M60" t="s">
         <v>22</v>
       </c>
       <c r="N60" t="s">
-        <v>278</v>
+        <v>79</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B61" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C61" t="s">
-        <v>168</v>
+        <v>53</v>
       </c>
       <c r="D61" t="s">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="E61" t="s">
-        <v>250</v>
+        <v>282</v>
       </c>
       <c r="F61" t="s">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="G61" t="s">
-        <v>250</v>
+        <v>282</v>
       </c>
       <c r="H61" t="s">
-        <v>280</v>
+        <v>78</v>
       </c>
       <c r="I61" t="s">
-        <v>250</v>
+        <v>282</v>
       </c>
       <c r="J61">
         <v>2</v>
@@ -3929,36 +3941,36 @@
         <v>22</v>
       </c>
       <c r="N61" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B62" t="s">
-        <v>75</v>
+        <v>285</v>
       </c>
       <c r="C62" t="s">
-        <v>53</v>
+        <v>167</v>
       </c>
       <c r="D62" t="s">
-        <v>282</v>
+        <v>76</v>
       </c>
       <c r="E62" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F62" t="s">
-        <v>282</v>
+        <v>76</v>
       </c>
       <c r="G62" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="H62" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="I62" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="J62">
         <v>2</v>
@@ -3973,7 +3985,7 @@
         <v>22</v>
       </c>
       <c r="N62" t="s">
-        <v>79</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>
